--- a/media/files/tools/shengri.xlsx
+++ b/media/files/tools/shengri.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
   <si>
     <t>姓名</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>岳芬</t>
+  </si>
+  <si>
+    <t>测试</t>
   </si>
 </sst>
 </file>
@@ -703,11 +706,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1021,7 +1027,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="18.125" customWidth="1"/>
@@ -1236,6 +1242,20 @@
       </c>
       <c r="D15" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46285</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46248</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/media/files/tools/shengri.xlsx
+++ b/media/files/tools/shengri.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
   <si>
     <t>姓名</t>
   </si>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t>岳芬</t>
-  </si>
-  <si>
-    <t>测试</t>
   </si>
 </sst>
 </file>
@@ -1245,18 +1242,8 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2">
-        <v>46285</v>
-      </c>
-      <c r="C16" s="2">
-        <v>46248</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1</v>
-      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/media/files/tools/shengri.xlsx
+++ b/media/files/tools/shengri.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
   <si>
     <t>姓名</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>岳芬</t>
+  </si>
+  <si>
+    <t>测试</t>
   </si>
 </sst>
 </file>
@@ -1242,8 +1245,18 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46285</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46248</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/media/files/tools/shengri.xlsx
+++ b/media/files/tools/shengri.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="26865" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,63 +34,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
   <si>
     <t>姓名</t>
   </si>
   <si>
+    <t>公历</t>
+  </si>
+  <si>
+    <t>农历</t>
+  </si>
+  <si>
+    <t>生日（公历/农历）</t>
+  </si>
+  <si>
+    <t>王小柏</t>
+  </si>
+  <si>
+    <t>李跃娣</t>
+  </si>
+  <si>
+    <t>王志斌</t>
+  </si>
+  <si>
+    <t>岳青</t>
+  </si>
+  <si>
+    <t>王伟</t>
+  </si>
+  <si>
+    <t>樊茹</t>
+  </si>
+  <si>
+    <t>王五仙</t>
+  </si>
+  <si>
+    <t>岳贵金</t>
+  </si>
+  <si>
+    <t>王一琳</t>
+  </si>
+  <si>
+    <t>王一博</t>
+  </si>
+  <si>
+    <t>王楚然</t>
+  </si>
+  <si>
+    <t>王姝越</t>
+  </si>
+  <si>
+    <t>岳杰</t>
+  </si>
+  <si>
+    <t>岳芬</t>
+  </si>
+  <si>
+    <t>测试</t>
+  </si>
+  <si>
     <t>阳历</t>
-  </si>
-  <si>
-    <t>阴历</t>
-  </si>
-  <si>
-    <t>生日（阴历/阳历）</t>
-  </si>
-  <si>
-    <t>王小柏</t>
-  </si>
-  <si>
-    <t>李跃娣</t>
-  </si>
-  <si>
-    <t>王志斌</t>
-  </si>
-  <si>
-    <t>岳青</t>
-  </si>
-  <si>
-    <t>王伟</t>
-  </si>
-  <si>
-    <t>樊茹</t>
-  </si>
-  <si>
-    <t>王五仙</t>
-  </si>
-  <si>
-    <t>岳贵金</t>
-  </si>
-  <si>
-    <t>王一琳</t>
-  </si>
-  <si>
-    <t>王一博</t>
-  </si>
-  <si>
-    <t>王楚然</t>
-  </si>
-  <si>
-    <t>王姝越</t>
-  </si>
-  <si>
-    <t>岳杰</t>
-  </si>
-  <si>
-    <t>岳芬</t>
-  </si>
-  <si>
-    <t>测试</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1258,7 @@
         <v>46248</v>
       </c>
       <c r="D16" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/media/files/tools/shengri.xlsx
+++ b/media/files/tools/shengri.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="26865" windowHeight="11775"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>姓名</t>
   </si>
@@ -93,7 +93,13 @@
     <t>测试</t>
   </si>
   <si>
-    <t>阳历</t>
+    <t>9月20日</t>
+  </si>
+  <si>
+    <t>8月14日</t>
+  </si>
+  <si>
+    <t>公立</t>
   </si>
 </sst>
 </file>
@@ -709,15 +715,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1038,227 +1050,227 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>21868</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>21837</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>21999</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>21973</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>30579</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2">
         <v>30542</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>31440</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2">
         <v>31400</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>31436</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="2">
         <v>31396</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>31723</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="2">
         <v>31565</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
         <v>21490</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="2">
         <v>21448</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="2">
         <v>23484</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="2">
         <v>23442</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="2">
         <v>40486</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="2">
         <v>40449</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2">
         <v>41577</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>41543</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="2">
         <v>45326</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="2">
         <v>45285</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="2">
         <v>45326</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="2">
         <v>45285</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="2">
         <v>33640</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>33640</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="2">
         <v>30595</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="2">
         <v>30560</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="2">
-        <v>46285</v>
-      </c>
-      <c r="C16" s="2">
-        <v>46248</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="B16" s="4" t="s">
         <v>19</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/media/files/tools/shengri.xlsx
+++ b/media/files/tools/shengri.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
   <si>
     <t>姓名</t>
   </si>
@@ -90,7 +90,7 @@
     <t>岳芬</t>
   </si>
   <si>
-    <t>测试</t>
+    <t>测试1</t>
   </si>
   <si>
     <t>9月20日</t>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>公立</t>
+  </si>
+  <si>
+    <t>测试2</t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1045,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="18.125" customWidth="1"/>
@@ -1270,6 +1273,18 @@
         <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="1" t="s">
         <v>21</v>
       </c>
     </row>
